--- a/ktds-kyra-guardrail/[KT DS] AI가드레일_구축_견적서_20260828.xlsx
+++ b/ktds-kyra-guardrail/[KT DS] AI가드레일_구축_견적서_20260828.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="견적서" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'견적서'!$A$1:$K$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'견적서'!$A$1:$K$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J31"/>
+  <dimension ref="B1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.77" customWidth="1" min="1" max="1"/>
@@ -981,24 +981,32 @@
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="11" t="n"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="206" customHeight="1">
       <c r="B17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>가드레일 엔진</t>
+          <t>KYRA
+AI Guardrail</t>
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>- 입력 · AI모델 동작 · 출력 3단계 다중화 가드레일
-  (단계별 민감정보 필터링, 적대적 공격 방어, 서비스 거부 공격 대응, 응답 결과 변형)</t>
+          <t>- AI 가드레일 구축 (KYRA AI Guardrail 1식)
+  · 입력 · AI모델 동작 · 출력 3단계 다중화 가드레일
+    (민감정보 필터링, 적대적 공격 방어, 서비스 거부 공격 대응, 응답 결과 변형)
+  · 프롬프트 인젝션 방어, 유해 콘텐츠 · 개인정보 · 기밀데이터 자동 검출 및 마스킹
+  · 응답 범위 제한(Topic Restriction), 사용자 권한별 기능 접근통제, 통합 관리 콘솔
+  · 비정상 쿼리 패턴 · 반복적 우회 시도 · 과도한 요청(Rate Abuse) 탐지 및 관리자 경보
+  · 전체 입·출력 이력 보존, 원인 추적 · 감사 기능, Syslog / SIEM 연동
+  · AI 플랫폼 탑재 및 다중망(AI망 · 운영망 · 개발망 · DMZ · AI개발망) 설치 · 구성,
+    운영자 교육 및 기술 이전</t>
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>24000000</v>
+        <v>70000000</v>
       </c>
       <c r="G17" s="16" t="n">
         <v>1</v>
@@ -1012,432 +1020,258 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>SEC-006</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="B18" s="12" t="n">
+          <t>SEC-006
+SEC-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="21">
+        <f>SUM(H17:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>콘텐츠 필터링</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>- 프롬프트 인젝션 방어, 유해 콘텐츠 · 개인정보 · 기밀데이터 자동 검출 및 마스킹</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="15">
-        <f>F18*G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>SEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="B19" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>정책 · 접근통제</t>
+          <t>재경비</t>
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>- 응답 범위 제한(Topic Restriction), 사용자 권한별 기능 접근통제, 통합 관리 콘솔</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="15">
-        <f>F19*G19</f>
-        <v/>
+          <t>- 제공 기술에 대한 일반 재경비 (본 견적 미적용)</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="I19" s="15" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>SEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
       <c r="B20" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>이상행위 모니터링</t>
+          <t>기술료</t>
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>- 비정상 쿼리 패턴 · 반복적 우회 시도 · 과도한 요청(Rate Abuse) 실시간 탐지 및 관리자 경보</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15">
-        <f>F20*G20</f>
-        <v/>
+          <t>- 제공 기술료 (본 견적 미적용)</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="I20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>SEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="B21" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>감사로그</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>- 전체 입·출력 이력 보존, 원인 추적 · 감사 기능, Syslog / SIEM 연동</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15">
-        <f>F21*G21</f>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="26">
+        <f>SUM(H19:H20)</f>
         <v/>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>SEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="B22" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>설치 · 기술이전</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>- AI 플랫폼 탑재 및 다중망(AI망 · 운영망 · 개발망 · DMZ · AI개발망) 설치 · 구성, 운영자 교육</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <f>F22*G22</f>
+      <c r="J21" s="27" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="31">
+        <f>H18+H21</f>
         <v/>
       </c>
-      <c r="I22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>SEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="21">
-        <f>SUM(H17:H22)</f>
+      <c r="I22" s="31">
+        <f>I18+I21</f>
         <v/>
       </c>
-      <c r="I23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>재경비</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>- 제공 기술에 대한 일반 재경비 (본 견적 미적용)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="B25" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>기술료</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>- 제공 기술료 (본 견적 미적용)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="26">
-        <f>SUM(H24:H25)</f>
+      <c r="J22" s="32" t="n"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>특별 견적 금액</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="34" t="n"/>
+      <c r="H23" s="35">
+        <f>H22</f>
         <v/>
       </c>
-      <c r="I26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="28" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="31">
-        <f>H23+H26</f>
+      <c r="I23" s="35">
+        <f>H22</f>
         <v/>
       </c>
-      <c r="I27" s="31">
-        <f>I23+I26</f>
+      <c r="J23" s="36" t="inlineStr">
+        <is>
+          <t>*할인률</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20.1" customHeight="1">
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="38" t="n"/>
+      <c r="J24" s="39">
+        <f>100%-(I23/H23)</f>
         <v/>
       </c>
-      <c r="J27" s="32" t="n"/>
-    </row>
-    <row r="28" ht="20.1" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>특별 견적 금액</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="n"/>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="34" t="n"/>
-      <c r="H28" s="35">
-        <f>H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="35">
-        <f>H27</f>
-        <v/>
-      </c>
-      <c r="J28" s="36" t="inlineStr">
-        <is>
-          <t>*할인률</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20.1" customHeight="1">
-      <c r="B29" s="37" t="n"/>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="38" t="n"/>
-      <c r="E29" s="38" t="n"/>
-      <c r="F29" s="38" t="n"/>
-      <c r="G29" s="38" t="n"/>
-      <c r="H29" s="38" t="n"/>
-      <c r="I29" s="38" t="n"/>
-      <c r="J29" s="39">
-        <f>100%-(I28/H28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="110" customHeight="1">
-      <c r="B30" s="40" t="inlineStr">
+    </row>
+    <row r="25" ht="94" customHeight="1">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>※ 비 고
-   - 본 견적은 공공사업 RFI 요건 SEC-006(AI시스템 가드레일 다중화 구성) 및 SEC-008(AI 플랫폼 내 가드레일 탑재) 대응 범위에 대한 견적이며, 각 항목의 대응 요건은 비고란에 표기하였습니다.
-   - 당사 KYRA AI Guardrail 제품을 모듈 단위 정액으로 산정하였으며, 재경비 및 기술료는 적용하지 않았습니다.
+   - 본 견적은 공공사업 RFI 요건 SEC-006(AI시스템 가드레일 다중화 구성) 및 SEC-008(AI 플랫폼 내 가드레일 탑재) 대응 범위에 대한 견적입니다.
+   - 당사 KYRA AI Guardrail 1식 정액으로 산정하였으며, 재경비 및 기술료는 적용하지 않았습니다.
    - 상기 금액은 부가가치세(VAT) 별도 금액이며, 계약 조건은 계약서에 따릅니다.
    - 서버·스토리지 등 하드웨어, 상용 LLM API 사용료, 타사 솔루션 라이선스 비용은 본 견적에 포함되어 있지 않습니다.</t>
         </is>
       </c>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="41" t="n"/>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="42" t="n"/>
-    </row>
-    <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="43" t="n"/>
-      <c r="C31" s="44" t="n"/>
-      <c r="D31" s="44" t="n"/>
-      <c r="E31" s="44" t="n"/>
-      <c r="F31" s="44" t="n"/>
-      <c r="G31" s="44" t="n"/>
-      <c r="H31" s="44" t="n"/>
-      <c r="I31" s="44" t="n"/>
-      <c r="J31" s="45" t="n"/>
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="41" t="n"/>
+      <c r="E25" s="41" t="n"/>
+      <c r="F25" s="41" t="n"/>
+      <c r="G25" s="41" t="n"/>
+      <c r="H25" s="41" t="n"/>
+      <c r="I25" s="41" t="n"/>
+      <c r="J25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="44" t="n"/>
+      <c r="H26" s="44" t="n"/>
+      <c r="I26" s="44" t="n"/>
+      <c r="J26" s="45" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="C24:D24"/>
+  <mergeCells count="17">
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B23:E24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B25:J26"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B30:J31"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B28:E29"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B4:F5"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:E22"/>
     <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/ktds-kyra-guardrail/[KT DS] AI가드레일_구축_견적서_20260828.xlsx
+++ b/ktds-kyra-guardrail/[KT DS] AI가드레일_구축_견적서_20260828.xlsx
@@ -836,7 +836,7 @@
     <row r="4" ht="31.5" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>케이티디에스(주) 귀중</t>
+          <t>주식회사 케이티디에스 귀중</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
     <row r="6" ht="23.25" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>견  적   명 : AI 가드레일 구축 (공공사업 RFI 요건 SEC-006 · SEC-008 대응)</t>
+          <t>견  적   명 : AI 가드레일 구축 (RFI 요건 SEC-006 · SEC-008 대응)</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="16" ht="39.95" customHeight="1">
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>AI 가드레일 구축 — KYRA AI Guardrail (다중화 가드레일 · AI 플랫폼 탑재)</t>
+          <t>AI 가드레일 구축 — KYRA AI Guardrail (다중화 가드레일 1식)</t>
         </is>
       </c>
       <c r="C16" s="10" t="n"/>
@@ -981,7 +981,7 @@
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="11" t="n"/>
     </row>
-    <row r="17" ht="206" customHeight="1">
+    <row r="17" ht="192" customHeight="1">
       <c r="B17" s="12" t="n">
         <v>1</v>
       </c>
@@ -1001,7 +1001,7 @@
   · 응답 범위 제한(Topic Restriction), 사용자 권한별 기능 접근통제, 통합 관리 콘솔
   · 비정상 쿼리 패턴 · 반복적 우회 시도 · 과도한 요청(Rate Abuse) 탐지 및 관리자 경보
   · 전체 입·출력 이력 보존, 원인 추적 · 감사 기능, Syslog / SIEM 연동
-  · AI 플랫폼 탑재 및 다중망(AI망 · 운영망 · 개발망 · DMZ · AI개발망) 설치 · 구성,
+  · 다중망(AI망 · 운영망 · 개발망 · DMZ · AI개발망) 설치 · 구성,
     운영자 교육 및 기술 이전</t>
         </is>
       </c>
@@ -1227,7 +1227,7 @@
       <c r="B25" s="40" t="inlineStr">
         <is>
           <t>※ 비 고
-   - 본 견적은 공공사업 RFI 요건 SEC-006(AI시스템 가드레일 다중화 구성) 및 SEC-008(AI 플랫폼 내 가드레일 탑재) 대응 범위에 대한 견적입니다.
+   - 본 견적은 RFI 요건 SEC-006(AI시스템 가드레일 다중화 구성) 및 SEC-008 대응 범위에 대한 견적입니다.
    - 당사 KYRA AI Guardrail 1식 정액으로 산정하였으며, 재경비 및 기술료는 적용하지 않았습니다.
    - 상기 금액은 부가가치세(VAT) 별도 금액이며, 계약 조건은 계약서에 따릅니다.
    - 서버·스토리지 등 하드웨어, 상용 LLM API 사용료, 타사 솔루션 라이선스 비용은 본 견적에 포함되어 있지 않습니다.</t>
